--- a/Codes/The_New_Codes/حالات الكود.xlsx
+++ b/Codes/The_New_Codes/حالات الكود.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5a843af4fc71c607/Desktop/JavaScript codes/Codes/The_New_Codes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1026" documentId="13_ncr:1_{1559862C-1BDB-4816-AF61-9B0D75B17520}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{307CDBF7-F2B3-40C6-9F9B-4ED915C7C0EC}"/>
+  <xr:revisionPtr revIDLastSave="1070" documentId="13_ncr:1_{1559862C-1BDB-4816-AF61-9B0D75B17520}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01C3E454-49E9-48C0-9E37-06311EB7509F}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-Form_Intail" sheetId="3" r:id="rId1"/>
@@ -1017,36 +1017,6 @@
     </dxf>
     <dxf>
       <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -1072,6 +1042,36 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
         <color theme="1"/>
         <name val="Calibri"/>
         <family val="2"/>
@@ -1263,25 +1263,25 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CA7804F7-4D49-464A-8A04-6E3E1DE6333B}" name="Table13" displayName="Table13" ref="A1:D20" totalsRowShown="0" headerRowDxfId="33" dataDxfId="32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CA7804F7-4D49-464A-8A04-6E3E1DE6333B}" name="Table13" displayName="Table13" ref="A1:D20" totalsRowShown="0" headerRowDxfId="45" dataDxfId="44">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{E3984B10-3F30-47B1-ADB3-BFF2449C9DC0}" name="اسم الحالة" dataDxfId="31" totalsRowDxfId="30"/>
-    <tableColumn id="2" xr3:uid="{018126E2-3097-40F5-AF0C-53F9343D9B94}" name="نوع الحالة" dataDxfId="29" totalsRowDxfId="28"/>
-    <tableColumn id="3" xr3:uid="{07667CF8-87E3-4130-9BA6-633C9C8EFF78}" name="البدايه من" dataDxfId="27" totalsRowDxfId="26"/>
-    <tableColumn id="4" xr3:uid="{0D53CCE0-BA21-4593-849F-F5CDD693C4A6}" name="النهايه في" dataDxfId="25" totalsRowDxfId="24"/>
+    <tableColumn id="1" xr3:uid="{E3984B10-3F30-47B1-ADB3-BFF2449C9DC0}" name="اسم الحالة" dataDxfId="43" totalsRowDxfId="42"/>
+    <tableColumn id="2" xr3:uid="{018126E2-3097-40F5-AF0C-53F9343D9B94}" name="نوع الحالة" dataDxfId="41" totalsRowDxfId="40"/>
+    <tableColumn id="3" xr3:uid="{07667CF8-87E3-4130-9BA6-633C9C8EFF78}" name="البدايه من" dataDxfId="39" totalsRowDxfId="38"/>
+    <tableColumn id="4" xr3:uid="{0D53CCE0-BA21-4593-849F-F5CDD693C4A6}" name="النهايه في" dataDxfId="37" totalsRowDxfId="36"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{11C54C73-4412-454C-9B06-6F8B2DE203AF}" name="Table1" displayName="Table1" ref="A1:E24" totalsRowShown="0" headerRowDxfId="45" dataDxfId="44">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{11C54C73-4412-454C-9B06-6F8B2DE203AF}" name="Table1" displayName="Table1" ref="A1:E24" totalsRowShown="0" headerRowDxfId="35" dataDxfId="34">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{A5A2981F-1590-4240-8C39-3DA4A7FC2DA5}" name="اسم الحالة" dataDxfId="43" totalsRowDxfId="42"/>
-    <tableColumn id="2" xr3:uid="{6F81B565-3407-4474-B277-A6B7D00F6414}" name="نوع الحالة" dataDxfId="41" totalsRowDxfId="40"/>
-    <tableColumn id="3" xr3:uid="{2BFAC376-6CDF-4FE5-B5B2-691B11FED706}" name="البدايه من" dataDxfId="39" totalsRowDxfId="38"/>
-    <tableColumn id="4" xr3:uid="{CFBA7893-BED2-4579-931D-9F394F1C35B4}" name="النهايه في" dataDxfId="37" totalsRowDxfId="36"/>
-    <tableColumn id="5" xr3:uid="{BCDE94CC-243F-49F0-8B54-F55ED5CEB809}" name="الملاحظات" dataDxfId="35" totalsRowDxfId="34"/>
+    <tableColumn id="1" xr3:uid="{A5A2981F-1590-4240-8C39-3DA4A7FC2DA5}" name="اسم الحالة" dataDxfId="33" totalsRowDxfId="32"/>
+    <tableColumn id="2" xr3:uid="{6F81B565-3407-4474-B277-A6B7D00F6414}" name="نوع الحالة" dataDxfId="31" totalsRowDxfId="30"/>
+    <tableColumn id="3" xr3:uid="{2BFAC376-6CDF-4FE5-B5B2-691B11FED706}" name="البدايه من" dataDxfId="29" totalsRowDxfId="28"/>
+    <tableColumn id="4" xr3:uid="{CFBA7893-BED2-4579-931D-9F394F1C35B4}" name="النهايه في" dataDxfId="27" totalsRowDxfId="26"/>
+    <tableColumn id="5" xr3:uid="{BCDE94CC-243F-49F0-8B54-F55ED5CEB809}" name="الملاحظات" dataDxfId="25" totalsRowDxfId="24"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1629,10 +1629,10 @@
         <v>51</v>
       </c>
       <c r="C2" s="1">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D2" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -1643,7 +1643,7 @@
         <v>52</v>
       </c>
       <c r="C3" s="1">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D3" s="1">
         <v>59</v>
@@ -1657,7 +1657,7 @@
         <v>53</v>
       </c>
       <c r="C4" s="1">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D4" s="1">
         <v>66</v>
@@ -1671,7 +1671,7 @@
         <v>54</v>
       </c>
       <c r="C5" s="1">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D5" s="1">
         <v>82</v>
@@ -1685,10 +1685,10 @@
         <v>55</v>
       </c>
       <c r="C6" s="1">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D6" s="1">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -1699,10 +1699,10 @@
         <v>56</v>
       </c>
       <c r="C7" s="1">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D7" s="1">
-        <v>144</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -1713,10 +1713,10 @@
         <v>58</v>
       </c>
       <c r="C8" s="1">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="D8" s="1">
-        <v>164</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -1727,10 +1727,10 @@
         <v>60</v>
       </c>
       <c r="C9" s="1">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="D9" s="1">
-        <v>194</v>
+        <v>210</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -1741,10 +1741,10 @@
         <v>61</v>
       </c>
       <c r="C10" s="1">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="D10" s="1">
-        <v>226</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -1755,10 +1755,10 @@
         <v>62</v>
       </c>
       <c r="C11" s="1">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="D11" s="1">
-        <v>258</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -1769,10 +1769,10 @@
         <v>103</v>
       </c>
       <c r="C12" s="1">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="D12" s="1">
-        <v>293</v>
+        <v>307</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -1783,10 +1783,10 @@
         <v>104</v>
       </c>
       <c r="C13" s="1">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="D13" s="1">
-        <v>329</v>
+        <v>341</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -1797,10 +1797,10 @@
         <v>105</v>
       </c>
       <c r="C14" s="1">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="D14" s="1">
-        <v>363</v>
+        <v>373</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -1811,10 +1811,10 @@
         <v>106</v>
       </c>
       <c r="C15" s="1">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="D15" s="1">
-        <v>399</v>
+        <v>407</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -1825,10 +1825,10 @@
         <v>109</v>
       </c>
       <c r="C16" s="1">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="D16" s="1">
-        <v>442</v>
+        <v>448</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -1839,10 +1839,10 @@
         <v>110</v>
       </c>
       <c r="C17" s="1">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="D17" s="1">
-        <v>458</v>
+        <v>464</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -1853,10 +1853,10 @@
         <v>111</v>
       </c>
       <c r="C18" s="1">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="D18" s="1">
-        <v>503</v>
+        <v>509</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -1867,10 +1867,10 @@
         <v>112</v>
       </c>
       <c r="C19" s="1">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="D19" s="1">
-        <v>522</v>
+        <v>528</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -1881,10 +1881,10 @@
         <v>113</v>
       </c>
       <c r="C20" s="1">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="D20" s="1">
-        <v>543</v>
+        <v>550</v>
       </c>
     </row>
   </sheetData>
@@ -1933,10 +1933,10 @@
         <v>6</v>
       </c>
       <c r="C2" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D2" s="1">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E2" s="1"/>
     </row>
@@ -1948,10 +1948,10 @@
         <v>5</v>
       </c>
       <c r="C3" s="1">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D3" s="1">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="E3" s="1"/>
     </row>
@@ -1963,10 +1963,10 @@
         <v>8</v>
       </c>
       <c r="C4" s="1">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D4" s="1">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="E4" s="1"/>
     </row>
@@ -1978,10 +1978,10 @@
         <v>10</v>
       </c>
       <c r="C5" s="1">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="D5" s="1">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="E5" s="1"/>
     </row>
